--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33933-2025 artfynd.xlsx
+++ b/artfynd/A 33933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414943</v>
       </c>
       <c r="B2" t="n">
-        <v>98387</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
